--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45183.57416001872</v>
+        <v>45252</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
@@ -885,20 +885,6 @@
       </c>
       <c r="C11" s="10" t="n"/>
     </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26" ht="13.5" customHeight="1" s="25">
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
@@ -958,7 +944,7 @@
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="18" t="n">
-        <v>56.403</v>
+        <v>62.043</v>
       </c>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
@@ -985,7 +971,7 @@
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="19" t="n">
-        <v>60.39</v>
+        <v>66.429</v>
       </c>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
@@ -1012,7 +998,7 @@
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="19" t="n">
-        <v>63.239</v>
+        <v>69.563</v>
       </c>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
@@ -1039,7 +1025,7 @@
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="19" t="n">
-        <v>66.373</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
@@ -1066,7 +1052,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="19" t="n">
-        <v>69.508</v>
+        <v>76.459</v>
       </c>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
@@ -1093,7 +1079,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="19" t="n">
-        <v>73.492</v>
+        <v>80.84099999999999</v>
       </c>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
@@ -1120,7 +1106,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="19" t="n">
-        <v>79.762</v>
+        <v>87.738</v>
       </c>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
@@ -1147,7 +1133,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="19" t="n">
-        <v>90.017</v>
+        <v>99.01900000000001</v>
       </c>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
@@ -1169,7 +1155,7 @@
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="19" t="n">
-        <v>105.4</v>
+        <v>115.94</v>
       </c>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
@@ -1203,7 +1189,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="13.5" customHeight="1" s="25">
       <c r="B42" s="8" t="inlineStr">
         <is>
@@ -1213,17 +1198,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B28:C28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -1198,17 +1198,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B29:C29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45252</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
@@ -1198,17 +1198,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45253</v>
+        <v>45254</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
@@ -1198,17 +1198,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B29:C29"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B31:C31"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45254</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>

--- a/LISTAS/ma/GANCHO J.xlsx
+++ b/LISTAS/ma/GANCHO J.xlsx
@@ -778,7 +778,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="24" t="n">
-        <v>45266</v>
+        <v>45264.54807695406</v>
       </c>
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
@@ -885,6 +885,20 @@
       </c>
       <c r="C11" s="10" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26" ht="13.5" customHeight="1" s="25">
       <c r="D26" s="5" t="n"/>
       <c r="E26" s="5" t="n"/>
@@ -944,7 +958,7 @@
       </c>
       <c r="C29" s="23" t="n"/>
       <c r="D29" s="18" t="n">
-        <v>62.043</v>
+        <v>82.55</v>
       </c>
       <c r="E29" s="5" t="n"/>
       <c r="F29" s="5" t="n"/>
@@ -971,7 +985,7 @@
       </c>
       <c r="C30" s="23" t="n"/>
       <c r="D30" s="19" t="n">
-        <v>66.429</v>
+        <v>88.38</v>
       </c>
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
@@ -998,7 +1012,7 @@
       </c>
       <c r="C31" s="23" t="n"/>
       <c r="D31" s="19" t="n">
-        <v>69.563</v>
+        <v>92.55</v>
       </c>
       <c r="E31" s="5" t="n"/>
       <c r="F31" s="5" t="n"/>
@@ -1025,7 +1039,7 @@
       </c>
       <c r="C32" s="23" t="n"/>
       <c r="D32" s="19" t="n">
-        <v>73.01000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="E32" s="5" t="n"/>
       <c r="F32" s="5" t="n"/>
@@ -1052,7 +1066,7 @@
       </c>
       <c r="C33" s="23" t="n"/>
       <c r="D33" s="19" t="n">
-        <v>76.459</v>
+        <v>101.73</v>
       </c>
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
@@ -1079,7 +1093,7 @@
       </c>
       <c r="C34" s="23" t="n"/>
       <c r="D34" s="19" t="n">
-        <v>80.84099999999999</v>
+        <v>107.56</v>
       </c>
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
@@ -1106,7 +1120,7 @@
       </c>
       <c r="C35" s="23" t="n"/>
       <c r="D35" s="19" t="n">
-        <v>87.738</v>
+        <v>116.74</v>
       </c>
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
@@ -1133,7 +1147,7 @@
       </c>
       <c r="C36" s="23" t="n"/>
       <c r="D36" s="19" t="n">
-        <v>99.01900000000001</v>
+        <v>131.75</v>
       </c>
       <c r="E36" s="5" t="n"/>
       <c r="F36" s="5" t="n"/>
@@ -1155,7 +1169,7 @@
       </c>
       <c r="C37" s="23" t="n"/>
       <c r="D37" s="19" t="n">
-        <v>115.94</v>
+        <v>154.26</v>
       </c>
       <c r="E37" s="5" t="n"/>
       <c r="F37" s="5" t="n"/>
@@ -1189,6 +1203,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42" ht="13.5" customHeight="1" s="25">
       <c r="B42" s="8" t="inlineStr">
         <is>
@@ -1198,17 +1213,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
